--- a/Result/profitability/1540.xlsx
+++ b/Result/profitability/1540.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>0.335</v>
+        <v>0.30875</v>
       </c>
       <c r="N2" t="n">
-        <v>31.02125</v>
+        <v>25.625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0.425</v>
+        <v>0.3525</v>
       </c>
       <c r="N3" t="n">
-        <v>28.49875</v>
+        <v>25.4325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.50625</v>
+        <v>0.43375</v>
       </c>
       <c r="N4" t="n">
-        <v>28.695</v>
+        <v>23.8125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6074999999999999</v>
+        <v>0.64375</v>
       </c>
       <c r="N5" t="n">
-        <v>27.6575</v>
+        <v>22.71375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.825</v>
+        <v>0.7637499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>27.0025</v>
+        <v>24.76</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>98.09999999999999</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.85375</v>
+        <v>0.7725</v>
       </c>
       <c r="N7" t="n">
-        <v>27.96875</v>
+        <v>23.14375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>0.85625</v>
+        <v>0.80625</v>
       </c>
       <c r="N8" t="n">
-        <v>26.8575</v>
+        <v>23.78</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>116</v>
+      </c>
+      <c r="D75" t="n">
+        <v>116</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-12.76%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.09375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-24.62</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.014003294892916</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7837837837837838</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-39.55</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.008671257332313</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
